--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.2.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.2.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.2.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.2.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y181"/>
+  <dimension ref="A1:Y194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -613,24 +613,28 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L5: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: THIS OFFICE: 一</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: ï»¿â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L4: isolated marker/symbol line :: ”</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: E</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -646,7 +650,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L506: line starts with punctuation glued to text :: .centre of the Moons shadow in this</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • en</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -681,7 +685,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>729</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -704,12 +708,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: THIS OFFICE: ä¸€</t>
+          <t>L84: stray/suspicious non-ASCII glyph(s): U+4E13 CJK UNIFIED IDEOGRAPH-4E13 | isolated marker/symbol line :: 专</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ en</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • en</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -721,7 +725,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L221: symbol-only separator/garbage line :: 000-</t>
+          <t>L139: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -737,14 +741,14 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L856: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aCoavia (odd internal casing) :: aCoavia him</t>
+          <t>L506: line starts with punctuation glued to text :: .centre of the Moons shadow in this</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr">
         <is>
-          <t>L902: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: â€”London Corres. N.O. Delta.</t>
+          <t>L902: abbreviation/spacing may be garbled :: —London Corres. N.O. Delta.</t>
         </is>
       </c>
       <c r="W3" s="1" t="inlineStr">
@@ -786,17 +790,17 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>L745: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): NewIPee (odd internal casing) :: General Walker Again.â€”The NewIPee like Lady Palmerstonâ€™s</t>
+          <t>L745: suspicious token(s): NewIPee (odd internal casing) :: General Walker Again.—The NewIPee like Lady Palmerston’s</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L37: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: known that there is a large tractâ€”al-</t>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+66F2 CJK UNIFIED IDEOGRAPH-66F2 | isolated marker/symbol line :: 曲</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: was informed it had been left byâ€¢</t>
+          <t>L17: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: was informed it had been left by•</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -808,7 +812,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L225: symbol-only separator/garbage line :: 528,00</t>
+          <t>L221: symbol-only separator/garbage line :: 000-</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -824,7 +828,7 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L907: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ---------------_-</t>
+          <t>L856: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aCoavia (odd internal casing) :: aCoavia him</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -846,12 +850,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>238</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>169</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -874,12 +878,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA | isolated marker/symbol line :: ä¸“</t>
+          <t>L209: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of age and an American by birth.â€”</t>
+          <t>L124: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: Tavern Licences,... •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -891,7 +895,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L227: symbol-only separator/garbage line :: 3,50</t>
+          <t>L225: symbol-only separator/garbage line :: 528,00</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -907,7 +911,7 @@
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L988: punctuation artifact: repeated periods | line starts with digit/letter garbage token | suspicious token(s): 2Deals (letter/digit mix), LaBarre (odd internal casing) | abbreviation/spacing may be garbled :: 2Deals to D.G. LaBarre Esq.... 2,56</t>
+          <t>L907: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ---------------_-</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -957,12 +961,12 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Cropss.- The Midge. â€” This</t>
+          <t>L218: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: form.â€”The annual meeting of the Abo-</t>
+          <t>L247: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -974,7 +978,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L229: symbol-only separator/garbage line :: 60,00</t>
+          <t>L227: symbol-only separator/garbage line :: 3,50</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
@@ -988,7 +992,11 @@
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>L988: punctuation artifact: repeated periods | line starts with digit/letter garbage token | suspicious token(s): 2Deals (letter/digit mix), LaBarre (odd internal casing) | abbreviation/spacing may be garbled :: 2Deals to D.G. LaBarre Esq.... 2,56</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
@@ -1036,12 +1044,12 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L111: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: years a hundred could be â€œshelled out."</t>
+          <t>L255: stray/suspicious non-ASCII glyph(s): U+7B49 CJK UNIFIED IDEOGRAPH-7B49 | isolated marker/symbol line :: 等</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: dians of Canada and Hudsonâ€™s Bay</t>
+          <t>L503: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: should be in print in that city before it _• 000 ...</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1053,7 +1061,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L231: symbol-only separator/garbage line :: 892,00</t>
+          <t>L229: symbol-only separator/garbage line :: 60,00</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -1111,24 +1119,24 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L233: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Merchant's Liquor Licence, â€¦, .</t>
+          <t>L267: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L70: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” BOOK AND JOB PRINTING</t>
+          <t>L874: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: to turn the wilderness into • fruitful cess which he has acheived in establish I transferred to the Hondurean Govern</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA | isolated marker/symbol line :: ä¸“</t>
+          <t>L84: stray/suspicious non-ASCII glyph(s): U+4E13 CJK UNIFIED IDEOGRAPH-4E13 | isolated marker/symbol line :: 专</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L247: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L231: symbol-only separator/garbage line :: 892,00</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -1138,7 +1146,7 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: 'Merchantâ€™s Liquor Licence,.... 512,0</t>
+          <t>L112: punctuation artifact: repeated periods :: 'Merchant’s Liquor Licence,.... 512,0</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1186,24 +1194,24 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L255: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN | isolated marker/symbol line :: ç­‰</t>
+          <t>L304: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: 'Merchantâ€™s Liquor Licence,.... 512,0</t>
+          <t>L956: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Maurice Sayer damage €</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L98: symbol-only separator/garbage line :: - 000</t>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+66F2 CJK UNIFIED IDEOGRAPH-66F2 | isolated marker/symbol line :: 曲</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L336: isolated marker/symbol line :: 15</t>
+          <t>L247: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr">
@@ -1233,12 +1241,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1261,24 +1269,24 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L259: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Pald to Ludger DEPAR â€¦ s</t>
+          <t>L399: stray/suspicious non-ASCII glyph(s): U+5B66 CJK UNIFIED IDEOGRAPH-5B66 | isolated marker/symbol line :: 学</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: Pedlarâ€™s Licence, ...................13,00</t>
+          <t>L1009: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: are not it is true very rich, but they Party.•</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L117: symbol-only separator/garbage line :: - 000</t>
+          <t>L98: symbol-only separator/garbage line :: - 000</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L339: symbol-only separator/garbage line :: $6375,09</t>
+          <t>L336: isolated marker/symbol line :: 15</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -1313,7 +1321,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1331,29 +1339,25 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>L878: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): IEastern (odd internal casing) :: _A_____1:-n....______________________: â€”._...IEastern. The docks, says a curres- ment ceapelied a Sardinian merchant.</t>
+          <t>L878: punctuation artifact: repeated periods | suspicious token(s): IEastern (odd internal casing) :: _A_____1:-n....______________________: —._...IEastern. The docks, says a curres- ment ceapelied a Sardinian merchant.</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L399: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+00A6 BROKEN BAR | isolated marker/symbol line :: å­¦</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: Tavern Licences,... â€¢</t>
-        </is>
-      </c>
+          <t>L417: stray/suspicious non-ASCII glyph(s): U+4E13 CJK UNIFIED IDEOGRAPH-4E13 | isolated marker/symbol line :: 专</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: 2</t>
+          <t>L117: symbol-only separator/garbage line :: - 000</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L358: isolated marker/symbol line :: 70</t>
+          <t>L339: symbol-only separator/garbage line :: $6375,09</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr">
@@ -1363,7 +1367,7 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: Pedlarâ€™s Licence, ...................13,00</t>
+          <t>L118: punctuation artifact: repeated periods :: Pedlar’s Licence, ...................13,00</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
@@ -1383,12 +1387,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>193</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1411,24 +1415,20 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L417: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA | isolated marker/symbol line :: ä¸“</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L151: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: property â€˜</t>
-        </is>
-      </c>
+          <t>L483: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L153: isolated marker/symbol line :: 10</t>
+          <t>L118: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L372: isolated marker/symbol line :: 10</t>
+          <t>L358: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1481,29 +1481,25 @@
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>L895: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): the28th (letter/digit mix) :: are concerned ; but it is the soil,â€” effect upon the base and slanderousingthe freedom of the Bay Islanders she wasnâ€™t Â°uch a big ship after all would commence on...</t>
+          <t>L895: suspicious token(s): the28th (letter/digit mix) :: are concerned ; but it is the soil,— effect upon the base and slanderousingthe freedom of the Bay Islanders she wasn’t °uch a big ship after all would commence on the2...</t>
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L436: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Solar Eclipse.â€” The path of the</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L180: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: known that there is a large tractâ€”al-</t>
-        </is>
-      </c>
+          <t>L484: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L204: isolated marker/symbol line :: e</t>
+          <t>L153: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L385: symbol-only separator/garbage line :: 75.00</t>
+          <t>L372: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1534,7 +1530,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1552,35 +1548,31 @@
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>L904: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | suspicious token(s): 1arlin (letter/digit mix) :: ------------|following are the contents : â€” The child, from seven to ten years old, that Newcastle Station of the Grand Trunk Proceedings of the English 1arlin-</t>
+          <t>L904: punctuation artifact: double/multiple hyphen | suspicious token(s): 1arlin (letter/digit mix) :: ------------|following are the contents : — The child, from seven to ten years old, that Newcastle Station of the Grand Trunk Proceedings of the English 1arlin-</t>
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L466: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Departure of the Japanese.â€” The</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L216: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Steamship United States ground except under the regulationsâ€”that the</t>
-        </is>
-      </c>
+          <t>L486: stray/suspicious non-ASCII glyph(s): U+603B CJK UNIFIED IDEOGRAPH-603B | isolated marker/symbol line :: 总</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L219: symbol-only separator/garbage line :: 422.16</t>
+          <t>L204: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L387: symbol-only separator/garbage line :: 18.69</t>
+          <t>L385: symbol-only separator/garbage line :: 75.00</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: Tavern Licences,... â€¢</t>
+          <t>L124: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: Tavern Licences,... •</t>
         </is>
       </c>
       <c r="R14" s="1" t="inlineStr"/>
@@ -1628,24 +1620,20 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L483: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L236: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Hollowayâ€™s Pills.â€”There is no ha-</t>
-        </is>
-      </c>
+          <t>L572: stray/suspicious non-ASCII glyph(s): U+91CF CJK UNIFIED IDEOGRAPH-91CF | isolated marker/symbol line :: 量</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L220: isolated marker/symbol line :: .</t>
+          <t>L209: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L389: symbol-only separator/garbage line :: 2.00</t>
+          <t>L387: symbol-only separator/garbage line :: 18.69</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1691,24 +1679,20 @@
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L486: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: æ€»</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L238: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Professor Hollowayâ€™s remediesin this</t>
-        </is>
-      </c>
+          <t>L603: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: Cora easier; Mixed 32； Yellow 32.</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L222: symbol-only separator/garbage line :: 14207</t>
+          <t>L218: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L456: symbol-only separator/garbage line :: 10.00</t>
+          <t>L389: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1750,30 +1734,26 @@
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>L539: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ing down smack on his headâ€”" Pam""</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L247: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+          <t>L690: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L224: isolated marker/symbol line :: **</t>
+          <t>L219: symbol-only separator/garbage line :: 422.16</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L458: isolated marker/symbol line :: 800</t>
+          <t>L456: symbol-only separator/garbage line :: 10.00</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>L353: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: rue. Esquireâ€™s barn, .....</t>
+          <t>L353: punctuation artifact: repeated periods :: rue. Esquire’s barn, .....</t>
         </is>
       </c>
       <c r="R17" s="1" t="inlineStr"/>
@@ -1797,24 +1777,20 @@
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>L551: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: DÃ©laine " (mousseline de laine;) and</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L249: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paid to AimÃ©</t>
-        </is>
-      </c>
+          <t>L703: stray/suspicious non-ASCII glyph(s): U+54C1 CJK UNIFIED IDEOGRAPH-54C1 | isolated marker/symbol line :: 品.</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L225: symbol-only separator/garbage line :: 3.10</t>
+          <t>L220: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L460: symbol-only separator/garbage line :: 4.00</t>
+          <t>L458: isolated marker/symbol line :: 800</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1844,24 +1820,20 @@
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>L561: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Boston Journal.</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L262: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Crops.â€” The Midge. â€” This</t>
-        </is>
-      </c>
+          <t>L710: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L227: isolated marker/symbol line :: .</t>
+          <t>L222: symbol-only separator/garbage line :: 14207</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L462: symbol-only separator/garbage line :: 15.6)</t>
+          <t>L460: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1891,24 +1863,20 @@
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>L572: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: é‡�</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L263: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: morning, says the St. Catherineâ€™s Jour-</t>
-        </is>
-      </c>
+          <t>L813: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L228: isolated marker/symbol line :: .</t>
+          <t>L224: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L464: symbol-only separator/garbage line :: 8.00</t>
+          <t>L462: symbol-only separator/garbage line :: 15.6)</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1938,24 +1906,20 @@
       <c r="I21" s="1" t="inlineStr"/>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>L574: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Personal.â€” â€” A report io current in</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L353: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: rue. Esquireâ€™s barn, .....</t>
-        </is>
-      </c>
+          <t>L848: stray/suspicious non-ASCII glyph(s): U+516B CJK UNIFIED IDEOGRAPH-516B | isolated marker/symbol line :: 八</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L229: symbol-only separator/garbage line :: 38.00</t>
+          <t>L225: symbol-only separator/garbage line :: 3.10</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L466: symbol-only separator/garbage line :: 5.00</t>
+          <t>L464: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1985,24 +1949,20 @@
       <c r="I22" s="1" t="inlineStr"/>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>L600: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Liverpool, Jope 23.â€” Breadstuffs.</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: tion No. Aâ€”.............</t>
-        </is>
-      </c>
+          <t>L862: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L231: symbol-only separator/garbage line :: 5.25</t>
+          <t>L227: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L468: symbol-only separator/garbage line :: 8.00</t>
+          <t>L466: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -2032,30 +1992,26 @@
       <c r="I23" s="1" t="inlineStr"/>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>L633: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Tie Grave of Eve.â€”In the old grave-</t>
-        </is>
-      </c>
+          <t>L904: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L232: symbol-only separator/garbage line :: 6.25</t>
+          <t>L228: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L470: isolated marker/symbol line :: 0</t>
+          <t>L468: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: tion No. Aâ€”.............</t>
+          <t>L412: punctuation artifact: repeated periods :: tion No. A—.............</t>
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr"/>
@@ -2079,24 +2035,20 @@
       <c r="I24" s="1" t="inlineStr"/>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>L643: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: To John Prouart. apprÃ©ciÃ©</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L483: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: moss-covered tombstone containing theâ€˜</t>
-        </is>
-      </c>
+          <t>L930: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: - 000 一</t>
+        </is>
+      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L234: symbol-only separator/garbage line :: 5120</t>
+          <t>L229: symbol-only separator/garbage line :: 38.00</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L520: symbol-only separator/garbage line :: 4 00</t>
+          <t>L470: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -2126,24 +2078,20 @@
       <c r="I25" s="1" t="inlineStr"/>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>L703: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: å“�.</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L484: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: following inscription :â€”</t>
-        </is>
-      </c>
+          <t>L950: stray/suspicious non-ASCII glyph(s): U+4E61 CJK UNIFIED IDEOGRAPH-4E61 | isolated marker/symbol line :: 乡</t>
+        </is>
+      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L236: symbol-only separator/garbage line :: 59, 66</t>
+          <t>L231: symbol-only separator/garbage line :: 5.25</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L521: isolated marker/symbol line :: 18</t>
+          <t>L520: symbol-only separator/garbage line :: 4 00</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -2173,24 +2121,20 @@
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>L761: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: about which there is no doubt â€” to</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L488: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: 28th, 1735, in ye 78th year of her age.â€�</t>
-        </is>
-      </c>
+          <t>L999: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L238: symbol-only separator/garbage line :: 383.25</t>
+          <t>L232: symbol-only separator/garbage line :: 6.25</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L523: symbol-only separator/garbage line :: 100.00</t>
+          <t>L521: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -2220,24 +2164,20 @@
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>L784: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: world â€” a system of which any country</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L489: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Boston Journal.</t>
-        </is>
-      </c>
+          <t>L1078: stray/suspicious non-ASCII glyph(s): U+51C6 CJK UNIFIED IDEOGRAPH-51C6 | isolated marker/symbol line :: 准</t>
+        </is>
+      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L240: symbol-only separator/garbage line :: 1100</t>
+          <t>L234: symbol-only separator/garbage line :: 5120</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L539: symbol-only separator/garbage line :: 24.00</t>
+          <t>L523: symbol-only separator/garbage line :: 100.00</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -2267,24 +2207,20 @@
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>L785: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: might well be proud â€” has laid Canada</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L503: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: should be in print in that city before it _â€¢ 000 ...</t>
-        </is>
-      </c>
+          <t>L1092: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L242: isolated marker/symbol line :: 700</t>
+          <t>L236: symbol-only separator/garbage line :: 59, 66</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L544: isolated marker/symbol line :: G.</t>
+          <t>L539: symbol-only separator/garbage line :: 24.00</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -2314,24 +2250,20 @@
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr">
         <is>
-          <t>L813: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L505: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: can be received at Quebec or Montreal, The Solar Eclipse.â€”Thepath of the</t>
-        </is>
-      </c>
+          <t>L1106: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L244: symbol-only separator/garbage line :: 42.97</t>
+          <t>L238: symbol-only separator/garbage line :: 383.25</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L560: isolated marker/symbol line :: 50</t>
+          <t>L544: isolated marker/symbol line :: G.</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2361,24 +2293,20 @@
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>L902: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: â€”London Corres. N.O. Delta.</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L514: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: setting limits to - : --= -----frhis â€” -</t>
-        </is>
-      </c>
+          <t>L1109: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L246: symbol-only separator/garbage line :: 528, 00</t>
+          <t>L240: symbol-only separator/garbage line :: 1100</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L562: symbol-only separator/garbage line :: 4.05</t>
+          <t>L560: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -2406,32 +2334,24 @@
       <c r="G31" s="1" t="inlineStr"/>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>L930: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: - 000 ä¸€</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L555: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œtotal darkness" at the above place</t>
-        </is>
-      </c>
+      <c r="J31" s="1" t="inlineStr"/>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L248: symbol-only separator/garbage line :: 3.50</t>
+          <t>L242: isolated marker/symbol line :: 700</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L566: isolated marker/symbol line :: J.</t>
+          <t>L562: symbol-only separator/garbage line :: 4.05</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>L503: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: should be in print in that city before it _â€¢ 000 ...</t>
+          <t>L503: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: should be in print in that city before it _• 000 ...</t>
         </is>
       </c>
       <c r="R31" s="1" t="inlineStr"/>
@@ -2453,32 +2373,24 @@
       <c r="G32" s="1" t="inlineStr"/>
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>L996: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L557: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the Moonâ€™s shadow, 100 miles or 50 to</t>
-        </is>
-      </c>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L250: symbol-only separator/garbage line :: 60, 00</t>
+          <t>L244: symbol-only separator/garbage line :: 42.97</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L576: symbol-only separator/garbage line :: 4 50</t>
+          <t>L566: isolated marker/symbol line :: J.</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
       <c r="Q32" s="1" t="inlineStr">
         <is>
-          <t>L514: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: setting limits to - : --= -----frhis â€” -</t>
+          <t>L514: punctuation artifact: double/multiple hyphen :: setting limits to - : --= -----frhis — -</t>
         </is>
       </c>
       <c r="R32" s="1" t="inlineStr"/>
@@ -2500,26 +2412,18 @@
       <c r="G33" s="1" t="inlineStr"/>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>L999: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L586: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Personal.â€”A report is current in</t>
-        </is>
-      </c>
+      <c r="J33" s="1" t="inlineStr"/>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L253: symbol-only separator/garbage line :: 892, 00</t>
+          <t>L246: symbol-only separator/garbage line :: 528, 00</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L578: isolated marker/symbol line :: 37</t>
+          <t>L576: symbol-only separator/garbage line :: 4 50</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2547,26 +2451,18 @@
       <c r="G34" s="1" t="inlineStr"/>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>L1106: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L593: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Englandâ€™s Premier.-Lord Palmerston</t>
-        </is>
-      </c>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L255: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN | isolated marker/symbol line :: ç­‰</t>
+          <t>L248: symbol-only separator/garbage line :: 3.50</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L580: isolated marker/symbol line :: 90</t>
+          <t>L578: isolated marker/symbol line :: 37</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2594,26 +2490,18 @@
       <c r="G35" s="1" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr">
-        <is>
-          <t>L1109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L677: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: perhaps $4,800 eachâ€”we suppose paid</t>
-        </is>
-      </c>
+      <c r="J35" s="1" t="inlineStr"/>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L257: symbol-only separator/garbage line :: 1906.30</t>
+          <t>L250: symbol-only separator/garbage line :: 60, 00</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L582: symbol-only separator/garbage line :: 1.00</t>
+          <t>L580: isolated marker/symbol line :: 90</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2642,21 +2530,17 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L678: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: quarterly, â€”the one for doing little or</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L260: isolated marker/symbol line :: 30</t>
+          <t>L253: symbol-only separator/garbage line :: 892, 00</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L584: isolated marker/symbol line :: 70</t>
+          <t>L582: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2685,21 +2569,17 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L682: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: What effect the mining excitement down Toronto University.â€”Ed. Wit."</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L264: isolated marker/symbol line :: 70</t>
+          <t>L255: stray/suspicious non-ASCII glyph(s): U+7B49 CJK UNIFIED IDEOGRAPH-7B49 | isolated marker/symbol line :: 等</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L625: symbol-only separator/garbage line :: 1.25</t>
+          <t>L584: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2728,21 +2608,17 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L706: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ing down smack on his headâ€”"Pam" Regiments for operations on land. All</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L269: symbol-only separator/garbage line :: 75.00</t>
+          <t>L257: symbol-only separator/garbage line :: 1906.30</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L627: symbol-only separator/garbage line :: 7.25</t>
+          <t>L625: symbol-only separator/garbage line :: 1.25</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2771,27 +2647,23 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L737: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Departure of the Japanese.â€” The</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L273: isolated marker/symbol line :: 00</t>
+          <t>L260: isolated marker/symbol line :: 30</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L628: isolated marker/symbol line :: **</t>
+          <t>L627: symbol-only separator/garbage line :: 7.25</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr">
         <is>
-          <t>L758: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: sees the requisite energy and industry ration of friends and foes ; and the sue- affords some slight interpretation ofthe â€”000--------</t>
+          <t>L758: punctuation artifact: double/multiple hyphen :: sees the requisite energy and industry ration of friends and foes ; and the sue- affords some slight interpretation ofthe —000--------</t>
         </is>
       </c>
       <c r="R39" s="1" t="inlineStr"/>
@@ -2814,27 +2686,23 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L745: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): NewIPee (odd internal casing) :: General Walker Again.â€”The NewIPee like Lady Palmerstonâ€™s</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L274: isolated marker/symbol line :: L</t>
+          <t>L264: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L630: symbol-only separator/garbage line :: 2.00</t>
+          <t>L628: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr">
         <is>
-          <t>L764: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: strongâ€™s fire, .............</t>
+          <t>L764: punctuation artifact: repeated periods :: strong’s fire, .............</t>
         </is>
       </c>
       <c r="R40" s="1" t="inlineStr"/>
@@ -2857,21 +2725,17 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L746: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Clem y eyed man of destiny,â€�leftdresses ? Because they are muzzling</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L280: symbol-only separator/garbage line :: 10.00</t>
+          <t>L267: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L632: isolated marker/symbol line :: P</t>
+          <t>L630: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -2900,21 +2764,17 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L758: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: sees the requisite energy and industry ration of friends and foes ; and the sue- affords some slight interpretation ofthe â€”000--------</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L284: isolated marker/symbol line :: 800</t>
+          <t>L269: symbol-only separator/garbage line :: 75.00</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L641: isolated marker/symbol line :: 000</t>
+          <t>L632: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -2943,21 +2803,17 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L764: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: strongâ€™s fire, .............</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L286: isolated marker/symbol line :: 400</t>
+          <t>L273: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L688: symbol-only separator/garbage line :: 16 00</t>
+          <t>L641: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -2986,21 +2842,17 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L803: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Liverpool, June *3. â€” Breadstuffâ€™s</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L289: isolated marker/symbol line :: .*</t>
+          <t>L274: isolated marker/symbol line :: L</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L690: symbol-only separator/garbage line :: 1.35</t>
+          <t>L688: symbol-only separator/garbage line :: 16 00</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -3029,21 +2881,17 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L813: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ashes quietâ€”Pots 27s 6d to 29 3d ;</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L290: symbol-only separator/garbage line :: 15.6)</t>
+          <t>L280: symbol-only separator/garbage line :: 10.00</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L694: isolated marker/symbol line :: F</t>
+          <t>L690: symbol-only separator/garbage line :: 1.35</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -3072,21 +2920,17 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L819: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London.â€”Money higher and active</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L296: isolated marker/symbol line :: T</t>
+          <t>L284: isolated marker/symbol line :: 800</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L695: isolated marker/symbol line :: J</t>
+          <t>L694: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -3115,27 +2959,23 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L874: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: to turn the wilderness into â€¢ fruitful cess which he has acheived in establish I transferred to the Hondurean Govern</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L319: symbol-only separator/garbage line :: 81.</t>
+          <t>L286: isolated marker/symbol line :: 400</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L697: isolated marker/symbol line :: a</t>
+          <t>L695: isolated marker/symbol line :: J</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr">
         <is>
-          <t>L876: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: sible that if mining is carried on with tion one of the most perfect and efficient [General Walker, in connecting himself, â€žâ€”.._._11_T_._.</t>
+          <t>L876: punctuation artifact: repeated periods :: sible that if mining is carried on with tion one of the most perfect and efficient [General Walker, in connecting himself, „—.._._11_T_._.</t>
         </is>
       </c>
       <c r="R47" s="1" t="inlineStr"/>
@@ -3158,27 +2998,23 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L876: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: sible that if mining is carried on with tion one of the most perfect and efficient [General Walker, in connecting himself, â€žâ€”.._._11_T_._.</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L324: symbol-only separator/garbage line :: 6375, 00</t>
+          <t>L289: isolated marker/symbol line :: .*</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L729: symbol-only separator/garbage line :: 1.00</t>
+          <t>L697: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
       <c r="Q48" s="1" t="inlineStr">
         <is>
-          <t>L878: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): IEastern (odd internal casing) :: _A_____1:-n....______________________: â€”._...IEastern. The docks, says a curres- ment ceapelied a Sardinian merchant.</t>
+          <t>L878: punctuation artifact: repeated periods | suspicious token(s): IEastern (odd internal casing) :: _A_____1:-n....______________________: —._...IEastern. The docks, says a curres- ment ceapelied a Sardinian merchant.</t>
         </is>
       </c>
       <c r="R48" s="1" t="inlineStr"/>
@@ -3201,21 +3037,17 @@
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L878: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): IEastern (odd internal casing) :: _A_____1:-n....______________________: â€”._...IEastern. The docks, says a curres- ment ceapelied a Sardinian merchant.</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L329: isolated marker/symbol line :: 1</t>
+          <t>L290: symbol-only separator/garbage line :: 15.6)</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L731: symbol-only separator/garbage line :: 2.00</t>
+          <t>L729: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
@@ -3244,27 +3076,23 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L881: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the attention of the public as to lead to worldâ€”a system of which any country tuated as much by an ultimate design of sp stators, the rigging of the ship- the harbou...</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L330: isolated marker/symbol line :: B</t>
+          <t>L296: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L733: symbol-only separator/garbage line :: 5.00</t>
+          <t>L731: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr"/>
       <c r="Q50" s="1" t="inlineStr">
         <is>
-          <t>L904: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | suspicious token(s): 1arlin (letter/digit mix) :: ------------|following are the contents : â€” The child, from seven to ten years old, that Newcastle Station of the Grand Trunk Proceedings of the English 1arlin-</t>
+          <t>L904: punctuation artifact: double/multiple hyphen | suspicious token(s): 1arlin (letter/digit mix) :: ------------|following are the contents : — The child, from seven to ten years old, that Newcastle Station of the Grand Trunk Proceedings of the English 1arlin-</t>
         </is>
       </c>
       <c r="R50" s="1" t="inlineStr"/>
@@ -3287,21 +3115,17 @@
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L882: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the neglect of those resources upon might well be proudâ€”has laid Canada Iragua as to punish Guardiola, the pre pingin the vicinity was filled with ad- Revenue the pa...</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L331: isolated marker/symbol line :: 0</t>
+          <t>L304: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr">
         <is>
-          <t>L735: symbol-only separator/garbage line :: 334.31</t>
+          <t>L733: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="P51" s="1" t="inlineStr"/>
@@ -3330,21 +3154,17 @@
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L889: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of no country rests on a sound founda- of his country's chief benefactors. Dr.is an unmitigated despotism, and the an irrevocable stupidity. They leanerdarmy after hav...</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L398: isolated marker/symbol line :: 2</t>
+          <t>L319: symbol-only separator/garbage line :: 81.</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr">
         <is>
-          <t>L834: symbol-only separator/garbage line :: 0.25</t>
+          <t>L735: symbol-only separator/garbage line :: 334.31</t>
         </is>
       </c>
       <c r="P52" s="1" t="inlineStr"/>
@@ -3373,21 +3193,17 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L895: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): the28th (letter/digit mix) :: are concerned ; but it is the soil,â€” effect upon the base and slanderousingthe freedom of the Bay Islanders she wasnâ€™t Â°uch a big ship after all would commence on...</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L399: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+00A6 BROKEN BAR | isolated marker/symbol line :: å­¦</t>
+          <t>L324: symbol-only separator/garbage line :: 6375, 00</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr">
         <is>
-          <t>L835: isolated marker/symbol line :: $</t>
+          <t>L834: symbol-only separator/garbage line :: 0.25</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr"/>
@@ -3416,27 +3232,23 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L902: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ^=^ he see an extensive Blackwoodâ€™s Magazine-The Juwecommand. â€” Robbing a Tracer -On Saterday of Baltimore." The Aperigan Minister</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L417: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA | isolated marker/symbol line :: ä¸“</t>
+          <t>L329: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr">
         <is>
-          <t>L845: isolated marker/symbol line :: E-</t>
+          <t>L835: isolated marker/symbol line :: $</t>
         </is>
       </c>
       <c r="P54" s="1" t="inlineStr"/>
       <c r="Q54" s="1" t="inlineStr">
         <is>
-          <t>L918: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Mr. I ouis Lampron ...........â€” 4,511</t>
+          <t>L918: punctuation artifact: repeated periods :: Mr. I ouis Lampron ...........— 4,511</t>
         </is>
       </c>
       <c r="R54" s="1" t="inlineStr"/>
@@ -3459,21 +3271,17 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L904: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | suspicious token(s): 1arlin (letter/digit mix) :: ------------|following are the contents : â€” The child, from seven to ten years old, that Newcastle Station of the Grand Trunk Proceedings of the English 1arlin-</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L482: isolated marker/symbol line :: 000</t>
+          <t>L330: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr">
         <is>
-          <t>L864: isolated marker/symbol line :: .:</t>
+          <t>L845: isolated marker/symbol line :: E-</t>
         </is>
       </c>
       <c r="P55" s="1" t="inlineStr"/>
@@ -3502,21 +3310,17 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L918: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Mr. I ouis Lampron ...........â€” 4,511</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L483: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L331: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr">
         <is>
-          <t>L865: symbol-only separator/garbage line :: 5,31</t>
+          <t>L864: isolated marker/symbol line :: .:</t>
         </is>
       </c>
       <c r="P56" s="1" t="inlineStr"/>
@@ -3545,21 +3349,17 @@
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L956: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: Maurice Sayer damage â‚¬</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L485: isolated marker/symbol line :: 000</t>
+          <t>L398: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr">
         <is>
-          <t>L866: isolated marker/symbol line :: -</t>
+          <t>L865: symbol-only separator/garbage line :: 5,31</t>
         </is>
       </c>
       <c r="P57" s="1" t="inlineStr"/>
@@ -3588,21 +3388,17 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L983: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: For M. Aaron Hart (RiviÃ¨re du</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L486: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: æ€»</t>
+          <t>L399: stray/suspicious non-ASCII glyph(s): U+5B66 CJK UNIFIED IDEOGRAPH-5B66 | isolated marker/symbol line :: 学</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr">
         <is>
-          <t>L867: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...10,80</t>
+          <t>L866: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P58" s="1" t="inlineStr"/>
@@ -3631,21 +3427,17 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L990: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: - Joseph Duval.â€” ................1,60:</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L487: symbol-only separator/garbage line :: - 000</t>
+          <t>L417: stray/suspicious non-ASCII glyph(s): U+4E13 CJK UNIFIED IDEOGRAPH-4E13 | isolated marker/symbol line :: 专</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr">
         <is>
-          <t>L869: symbol-only separator/garbage line :: 5,00</t>
+          <t>L867: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...10,80</t>
         </is>
       </c>
       <c r="P59" s="1" t="inlineStr"/>
@@ -3674,21 +3466,17 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L995: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Antoine DÃ©lorier 4 do. 24,00</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L488: isolated marker/symbol line :: 000</t>
+          <t>L482: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
         <is>
-          <t>L870: symbol-only separator/garbage line :: .... 750</t>
+          <t>L869: symbol-only separator/garbage line :: 5,00</t>
         </is>
       </c>
       <c r="P60" s="1" t="inlineStr"/>
@@ -3717,21 +3505,17 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L1005: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The extent end richness of the mine of clair.â€”Part V. Scottish National Cha"</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L495: isolated marker/symbol line :: 1</t>
+          <t>L483: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr">
         <is>
-          <t>L871: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 20,00</t>
+          <t>L870: symbol-only separator/garbage line :: .... 750</t>
         </is>
       </c>
       <c r="P61" s="1" t="inlineStr"/>
@@ -3760,21 +3544,17 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L1009: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: are not it is true very rich, but they Party.â€¢</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L530: isolated marker/symbol line :: D</t>
+          <t>L484: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr">
         <is>
-          <t>L907: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ---------------_-</t>
+          <t>L871: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 20,00</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr"/>
@@ -3803,21 +3583,17 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L1013: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: quote/punctuation debris :: from Peterboroâ€™, and mysteriously dis-steamerleft.,â€”., .â€ž</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L572: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: é‡�</t>
+          <t>L485: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
         <is>
-          <t>L929: symbol-only separator/garbage line :: $116,374</t>
+          <t>L907: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ---------------_-</t>
         </is>
       </c>
       <c r="P63" s="1" t="inlineStr"/>
@@ -3846,21 +3622,17 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L1026: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: -â€˜</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L587: isolated marker/symbol line :: d.</t>
+          <t>L486: stray/suspicious non-ASCII glyph(s): U+603B CJK UNIFIED IDEOGRAPH-603B | isolated marker/symbol line :: 总</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr">
         <is>
-          <t>L947: symbol-only separator/garbage line :: 1,00</t>
+          <t>L929: symbol-only separator/garbage line :: $116,374</t>
         </is>
       </c>
       <c r="P64" s="1" t="inlineStr"/>
@@ -3894,12 +3666,12 @@
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L607: symbol-only separator/garbage line :: 8.00</t>
+          <t>L487: symbol-only separator/garbage line :: - 000</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr">
         <is>
-          <t>L949: isolated marker/symbol line :: 1</t>
+          <t>L947: symbol-only separator/garbage line :: 1,00</t>
         </is>
       </c>
       <c r="P65" s="1" t="inlineStr"/>
@@ -3933,12 +3705,12 @@
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L610: isolated marker/symbol line :: *</t>
+          <t>L488: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr">
         <is>
-          <t>L951: symbol-only separator/garbage line :: 5,1</t>
+          <t>L949: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P66" s="1" t="inlineStr"/>
@@ -3972,18 +3744,18 @@
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L611: symbol-only separator/garbage line :: 5.00</t>
+          <t>L495: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr">
         <is>
-          <t>L960: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 20,00</t>
+          <t>L951: symbol-only separator/garbage line :: 5,1</t>
         </is>
       </c>
       <c r="P67" s="1" t="inlineStr"/>
       <c r="Q67" s="1" t="inlineStr">
         <is>
-          <t>L990: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: - Joseph Duval.â€” ................1,60:</t>
+          <t>L990: punctuation artifact: repeated periods :: - Joseph Duval.— ................1,60:</t>
         </is>
       </c>
       <c r="R67" s="1" t="inlineStr"/>
@@ -4011,12 +3783,12 @@
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L619: isolated marker/symbol line :: 400</t>
+          <t>L530: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr">
         <is>
-          <t>L961: isolated marker/symbol line :: - #</t>
+          <t>L960: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 20,00</t>
         </is>
       </c>
       <c r="P68" s="1" t="inlineStr"/>
@@ -4050,12 +3822,12 @@
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L623: symbol-only separator/garbage line :: 100.00</t>
+          <t>L572: stray/suspicious non-ASCII glyph(s): U+91CF CJK UNIFIED IDEOGRAPH-91CF | isolated marker/symbol line :: 量</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr">
         <is>
-          <t>L969: symbol-only separator/garbage line :: 220,00</t>
+          <t>L961: isolated marker/symbol line :: - #</t>
         </is>
       </c>
       <c r="P69" s="1" t="inlineStr"/>
@@ -4089,20 +3861,16 @@
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L627: isolated marker/symbol line :: **</t>
+          <t>L587: isolated marker/symbol line :: d.</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr">
         <is>
-          <t>L970: symbol-only separator/garbage line :: 6,00</t>
+          <t>L969: symbol-only separator/garbage line :: 220,00</t>
         </is>
       </c>
       <c r="P70" s="1" t="inlineStr"/>
-      <c r="Q70" s="1" t="inlineStr">
-        <is>
-          <t>L1013: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: quote/punctuation debris :: from Peterboroâ€™, and mysteriously dis-steamerleft.,â€”., .â€ž</t>
-        </is>
-      </c>
+      <c r="Q70" s="1" t="inlineStr"/>
       <c r="R70" s="1" t="inlineStr"/>
       <c r="S70" s="1" t="inlineStr"/>
       <c r="T70" s="1" t="inlineStr"/>
@@ -4128,12 +3896,12 @@
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L628: isolated marker/symbol line :: .</t>
+          <t>L607: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr">
         <is>
-          <t>L999: isolated marker/symbol line :: 0</t>
+          <t>L970: symbol-only separator/garbage line :: 6,00</t>
         </is>
       </c>
       <c r="P71" s="1" t="inlineStr"/>
@@ -4163,12 +3931,12 @@
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L629: symbol-only separator/garbage line :: 94.00</t>
+          <t>L610: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr">
         <is>
-          <t>L1001: symbol-only separator/garbage line :: 9,16</t>
+          <t>L999: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P72" s="1" t="inlineStr"/>
@@ -4198,12 +3966,12 @@
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L633: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L611: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr">
         <is>
-          <t>L1022: isolated marker/symbol line :: %</t>
+          <t>L1001: symbol-only separator/garbage line :: 9,16</t>
         </is>
       </c>
       <c r="P73" s="1" t="inlineStr"/>
@@ -4233,12 +4001,12 @@
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L636: isolated marker/symbol line :: 06</t>
+          <t>L619: isolated marker/symbol line :: 400</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr">
         <is>
-          <t>L1024: isolated marker/symbol line :: -</t>
+          <t>L1022: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P74" s="1" t="inlineStr"/>
@@ -4268,12 +4036,12 @@
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L645: isolated marker/symbol line :: *</t>
+          <t>L623: symbol-only separator/garbage line :: 100.00</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr">
         <is>
-          <t>L1028: isolated marker/symbol line :: a</t>
+          <t>L1024: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P75" s="1" t="inlineStr"/>
@@ -4303,12 +4071,12 @@
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L646: isolated marker/symbol line :: 0</t>
+          <t>L627: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr">
         <is>
-          <t>L1030: isolated marker/symbol line :: ,</t>
+          <t>L1026: isolated marker/symbol line :: -‘</t>
         </is>
       </c>
       <c r="P76" s="1" t="inlineStr"/>
@@ -4338,12 +4106,12 @@
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L647: isolated marker/symbol line :: 1</t>
+          <t>L628: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr">
         <is>
-          <t>L1032: isolated marker/symbol line :: -1</t>
+          <t>L1028: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P77" s="1" t="inlineStr"/>
@@ -4373,12 +4141,12 @@
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L649: isolated marker/symbol line :: 3</t>
+          <t>L629: symbol-only separator/garbage line :: 94.00</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr">
         <is>
-          <t>L1034: isolated marker/symbol line :: %</t>
+          <t>L1030: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="P78" s="1" t="inlineStr"/>
@@ -4408,12 +4176,12 @@
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L656: isolated marker/symbol line :: 8</t>
+          <t>L633: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr">
         <is>
-          <t>L1036: isolated marker/symbol line :: 1</t>
+          <t>L1032: isolated marker/symbol line :: -1</t>
         </is>
       </c>
       <c r="P79" s="1" t="inlineStr"/>
@@ -4443,12 +4211,12 @@
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L657: isolated marker/symbol line :: *</t>
+          <t>L636: isolated marker/symbol line :: 06</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
-          <t>L1038: isolated marker/symbol line :: %</t>
+          <t>L1034: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P80" s="1" t="inlineStr"/>
@@ -4478,12 +4246,12 @@
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L659: isolated marker/symbol line :: 2</t>
+          <t>L645: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr">
         <is>
-          <t>L1040: isolated marker/symbol line :: %</t>
+          <t>L1036: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P81" s="1" t="inlineStr"/>
@@ -4513,10 +4281,14 @@
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L664: isolated marker/symbol line :: 4</t>
-        </is>
-      </c>
-      <c r="O82" s="1" t="inlineStr"/>
+          <t>L646: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
+      <c r="O82" s="1" t="inlineStr">
+        <is>
+          <t>L1038: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P82" s="1" t="inlineStr"/>
       <c r="Q82" s="1" t="inlineStr"/>
       <c r="R82" s="1" t="inlineStr"/>
@@ -4544,10 +4316,14 @@
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L666: symbol-only separator/garbage line :: 2.00</t>
-        </is>
-      </c>
-      <c r="O83" s="1" t="inlineStr"/>
+          <t>L647: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O83" s="1" t="inlineStr">
+        <is>
+          <t>L1040: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P83" s="1" t="inlineStr"/>
       <c r="Q83" s="1" t="inlineStr"/>
       <c r="R83" s="1" t="inlineStr"/>
@@ -4575,7 +4351,7 @@
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L670: symbol-only separator/garbage line :: 1600</t>
+          <t>L649: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr"/>
@@ -4606,7 +4382,7 @@
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L674: isolated marker/symbol line :: 1</t>
+          <t>L656: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr"/>
@@ -4637,7 +4413,7 @@
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L678: isolated marker/symbol line :: 25</t>
+          <t>L657: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr"/>
@@ -4668,7 +4444,7 @@
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L679: isolated marker/symbol line :: 8</t>
+          <t>L659: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr"/>
@@ -4699,7 +4475,7 @@
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L682: symbol-only separator/garbage line :: 1.00</t>
+          <t>L664: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr"/>
@@ -4730,7 +4506,7 @@
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L685: symbol-only separator/garbage line :: 2.00</t>
+          <t>L666: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr"/>
@@ -4761,7 +4537,7 @@
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L689: symbol-only separator/garbage line :: 5.00</t>
+          <t>L670: symbol-only separator/garbage line :: 1600</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr"/>
@@ -4792,7 +4568,7 @@
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L691: isolated marker/symbol line :: S</t>
+          <t>L674: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr"/>
@@ -4823,7 +4599,7 @@
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L692: isolated marker/symbol line :: 3</t>
+          <t>L678: isolated marker/symbol line :: 25</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr"/>
@@ -4854,7 +4630,7 @@
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L694: symbol-only separator/garbage line :: 30131</t>
+          <t>L679: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr"/>
@@ -4885,7 +4661,7 @@
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L700: isolated marker/symbol line :: A</t>
+          <t>L682: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr"/>
@@ -4916,7 +4692,7 @@
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L702: isolated marker/symbol line :: 2</t>
+          <t>L685: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr"/>
@@ -4947,7 +4723,7 @@
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L704: symbol-only separator/garbage line :: 9555</t>
+          <t>L689: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr"/>
@@ -4978,7 +4754,7 @@
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L707: isolated marker/symbol line :: S</t>
+          <t>L690: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr"/>
@@ -5009,7 +4785,7 @@
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L708: isolated marker/symbol line :: 4</t>
+          <t>L691: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr"/>
@@ -5040,7 +4816,7 @@
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L712: isolated marker/symbol line :: 1</t>
+          <t>L692: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr"/>
@@ -5071,7 +4847,7 @@
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L713: isolated marker/symbol line :: 120</t>
+          <t>L694: symbol-only separator/garbage line :: 30131</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr"/>
@@ -5102,7 +4878,7 @@
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L716: symbol-only separator/garbage line :: 3, 00</t>
+          <t>L700: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr"/>
@@ -5133,7 +4909,7 @@
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L718: symbol-only separator/garbage line :: 8.25</t>
+          <t>L702: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr"/>
@@ -5164,7 +4940,7 @@
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L720: isolated marker/symbol line :: 531</t>
+          <t>L703: stray/suspicious non-ASCII glyph(s): U+54C1 CJK UNIFIED IDEOGRAPH-54C1 | isolated marker/symbol line :: 品.</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr"/>
@@ -5195,7 +4971,7 @@
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L729: isolated marker/symbol line :: G</t>
+          <t>L704: symbol-only separator/garbage line :: 9555</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr"/>
@@ -5226,7 +5002,7 @@
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L732: isolated marker/symbol line :: D</t>
+          <t>L707: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr"/>
@@ -5257,7 +5033,7 @@
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L733: isolated marker/symbol line :: 9</t>
+          <t>L708: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr"/>
@@ -5288,7 +5064,7 @@
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L735: isolated marker/symbol line :: C</t>
+          <t>L710: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr"/>
@@ -5319,7 +5095,7 @@
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L736: isolated marker/symbol line :: 000</t>
+          <t>L712: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr"/>
@@ -5350,7 +5126,7 @@
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L743: isolated marker/symbol line :: C</t>
+          <t>L713: isolated marker/symbol line :: 120</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr"/>
@@ -5381,7 +5157,7 @@
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L744: isolated marker/symbol line :: 4</t>
+          <t>L716: symbol-only separator/garbage line :: 3, 00</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr"/>
@@ -5412,7 +5188,7 @@
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L810: isolated marker/symbol line :: 4</t>
+          <t>L718: symbol-only separator/garbage line :: 8.25</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr"/>
@@ -5443,7 +5219,7 @@
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L812: isolated marker/symbol line :: A</t>
+          <t>L720: isolated marker/symbol line :: 531</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr"/>
@@ -5474,7 +5250,7 @@
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>L813: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L729: isolated marker/symbol line :: G</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr"/>
@@ -5505,7 +5281,7 @@
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>L816: isolated marker/symbol line :: 4</t>
+          <t>L732: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr"/>
@@ -5536,7 +5312,7 @@
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>L848: isolated marker/symbol line :: å…«</t>
+          <t>L733: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr"/>
@@ -5567,7 +5343,7 @@
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>L861: symbol-only separator/garbage line :: _ 000</t>
+          <t>L735: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr"/>
@@ -5598,7 +5374,7 @@
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>L903: isolated marker/symbol line :: 000</t>
+          <t>L736: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr"/>
@@ -5629,7 +5405,7 @@
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>L931: isolated marker/symbol line :: 00</t>
+          <t>L743: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr"/>
@@ -5660,7 +5436,7 @@
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
         <is>
-          <t>L947: isolated marker/symbol line :: 2</t>
+          <t>L744: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O119" s="1" t="inlineStr"/>
@@ -5691,7 +5467,7 @@
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
         <is>
-          <t>L951: isolated marker/symbol line :: '</t>
+          <t>L810: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O120" s="1" t="inlineStr"/>
@@ -5722,7 +5498,7 @@
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
         <is>
-          <t>L960: isolated marker/symbol line :: -</t>
+          <t>L812: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O121" s="1" t="inlineStr"/>
@@ -5753,7 +5529,7 @@
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
         <is>
-          <t>L965: isolated marker/symbol line :: A</t>
+          <t>L813: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O122" s="1" t="inlineStr"/>
@@ -5784,7 +5560,7 @@
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
         <is>
-          <t>L992: isolated marker/symbol line :: 4</t>
+          <t>L816: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O123" s="1" t="inlineStr"/>
@@ -5815,7 +5591,7 @@
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
         <is>
-          <t>L996: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L848: stray/suspicious non-ASCII glyph(s): U+516B CJK UNIFIED IDEOGRAPH-516B | isolated marker/symbol line :: 八</t>
         </is>
       </c>
       <c r="O124" s="1" t="inlineStr"/>
@@ -5846,7 +5622,7 @@
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
         <is>
-          <t>L999: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L861: symbol-only separator/garbage line :: _ 000</t>
         </is>
       </c>
       <c r="O125" s="1" t="inlineStr"/>
@@ -5877,7 +5653,7 @@
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
         <is>
-          <t>L1000: isolated marker/symbol line :: 313</t>
+          <t>L862: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O126" s="1" t="inlineStr"/>
@@ -5908,7 +5684,7 @@
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
         <is>
-          <t>L1003: symbol-only separator/garbage line :: 10.80</t>
+          <t>L903: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O127" s="1" t="inlineStr"/>
@@ -5939,7 +5715,7 @@
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
         <is>
-          <t>L1005: isolated marker/symbol line :: 2</t>
+          <t>L904: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O128" s="1" t="inlineStr"/>
@@ -5970,7 +5746,7 @@
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr">
         <is>
-          <t>L1007: symbol-only separator/garbage line :: 5.00</t>
+          <t>L931: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O129" s="1" t="inlineStr"/>
@@ -6001,7 +5777,7 @@
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr">
         <is>
-          <t>L1009: symbol-only separator/garbage line :: 7,50</t>
+          <t>L947: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O130" s="1" t="inlineStr"/>
@@ -6032,7 +5808,7 @@
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr">
         <is>
-          <t>L1010: isolated marker/symbol line :: 750</t>
+          <t>L950: stray/suspicious non-ASCII glyph(s): U+4E61 CJK UNIFIED IDEOGRAPH-4E61 | isolated marker/symbol line :: 乡</t>
         </is>
       </c>
       <c r="O131" s="1" t="inlineStr"/>
@@ -6063,7 +5839,7 @@
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr">
         <is>
-          <t>L1014: symbol-only separator/garbage line :: 20.00</t>
+          <t>L951: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O132" s="1" t="inlineStr"/>
@@ -6094,7 +5870,7 @@
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr">
         <is>
-          <t>L1016: symbol-only separator/garbage line :: 5.60</t>
+          <t>L960: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O133" s="1" t="inlineStr"/>
@@ -6125,7 +5901,7 @@
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr">
         <is>
-          <t>L1018: isolated marker/symbol line :: 250</t>
+          <t>L965: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O134" s="1" t="inlineStr"/>
@@ -6156,7 +5932,7 @@
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr">
         <is>
-          <t>L1020: symbol-only separator/garbage line :: 2.00</t>
+          <t>L992: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O135" s="1" t="inlineStr"/>
@@ -6187,7 +5963,7 @@
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr">
         <is>
-          <t>L1022: isolated marker/symbol line :: 4</t>
+          <t>L996: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O136" s="1" t="inlineStr"/>
@@ -6218,7 +5994,7 @@
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr">
         <is>
-          <t>L1023: isolated marker/symbol line :: 3</t>
+          <t>L999: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O137" s="1" t="inlineStr"/>
@@ -6249,7 +6025,7 @@
       <c r="M138" s="1" t="inlineStr"/>
       <c r="N138" s="1" t="inlineStr">
         <is>
-          <t>L1024: isolated marker/symbol line :: 112</t>
+          <t>L1000: isolated marker/symbol line :: 313</t>
         </is>
       </c>
       <c r="O138" s="1" t="inlineStr"/>
@@ -6280,7 +6056,7 @@
       <c r="M139" s="1" t="inlineStr"/>
       <c r="N139" s="1" t="inlineStr">
         <is>
-          <t>L1026: isolated marker/symbol line :: 1</t>
+          <t>L1003: symbol-only separator/garbage line :: 10.80</t>
         </is>
       </c>
       <c r="O139" s="1" t="inlineStr"/>
@@ -6311,7 +6087,7 @@
       <c r="M140" s="1" t="inlineStr"/>
       <c r="N140" s="1" t="inlineStr">
         <is>
-          <t>L1027: symbol-only separator/garbage line :: 11.</t>
+          <t>L1005: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O140" s="1" t="inlineStr"/>
@@ -6342,7 +6118,7 @@
       <c r="M141" s="1" t="inlineStr"/>
       <c r="N141" s="1" t="inlineStr">
         <is>
-          <t>L1030: isolated marker/symbol line :: 451</t>
+          <t>L1007: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O141" s="1" t="inlineStr"/>
@@ -6373,7 +6149,7 @@
       <c r="M142" s="1" t="inlineStr"/>
       <c r="N142" s="1" t="inlineStr">
         <is>
-          <t>L1032: isolated marker/symbol line :: 12</t>
+          <t>L1009: symbol-only separator/garbage line :: 7,50</t>
         </is>
       </c>
       <c r="O142" s="1" t="inlineStr"/>
@@ -6404,7 +6180,7 @@
       <c r="M143" s="1" t="inlineStr"/>
       <c r="N143" s="1" t="inlineStr">
         <is>
-          <t>L1033: isolated marker/symbol line :: D</t>
+          <t>L1010: isolated marker/symbol line :: 750</t>
         </is>
       </c>
       <c r="O143" s="1" t="inlineStr"/>
@@ -6435,7 +6211,7 @@
       <c r="M144" s="1" t="inlineStr"/>
       <c r="N144" s="1" t="inlineStr">
         <is>
-          <t>L1035: symbol-only separator/garbage line :: 7.10</t>
+          <t>L1014: symbol-only separator/garbage line :: 20.00</t>
         </is>
       </c>
       <c r="O144" s="1" t="inlineStr"/>
@@ -6466,7 +6242,7 @@
       <c r="M145" s="1" t="inlineStr"/>
       <c r="N145" s="1" t="inlineStr">
         <is>
-          <t>L1037: isolated marker/symbol line :: 3</t>
+          <t>L1016: symbol-only separator/garbage line :: 5.60</t>
         </is>
       </c>
       <c r="O145" s="1" t="inlineStr"/>
@@ -6497,7 +6273,7 @@
       <c r="M146" s="1" t="inlineStr"/>
       <c r="N146" s="1" t="inlineStr">
         <is>
-          <t>L1039: symbol-only separator/garbage line :: 2, 00</t>
+          <t>L1018: isolated marker/symbol line :: 250</t>
         </is>
       </c>
       <c r="O146" s="1" t="inlineStr"/>
@@ -6528,7 +6304,7 @@
       <c r="M147" s="1" t="inlineStr"/>
       <c r="N147" s="1" t="inlineStr">
         <is>
-          <t>L1041: symbol-only separator/garbage line :: 6, 60</t>
+          <t>L1020: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="O147" s="1" t="inlineStr"/>
@@ -6559,7 +6335,7 @@
       <c r="M148" s="1" t="inlineStr"/>
       <c r="N148" s="1" t="inlineStr">
         <is>
-          <t>L1043: symbol-only separator/garbage line :: $116, 371</t>
+          <t>L1022: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O148" s="1" t="inlineStr"/>
@@ -6590,7 +6366,7 @@
       <c r="M149" s="1" t="inlineStr"/>
       <c r="N149" s="1" t="inlineStr">
         <is>
-          <t>L1046: symbol-only separator/garbage line :: 1.00</t>
+          <t>L1023: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O149" s="1" t="inlineStr"/>
@@ -6621,7 +6397,7 @@
       <c r="M150" s="1" t="inlineStr"/>
       <c r="N150" s="1" t="inlineStr">
         <is>
-          <t>L1048: isolated marker/symbol line :: 65</t>
+          <t>L1024: isolated marker/symbol line :: 112</t>
         </is>
       </c>
       <c r="O150" s="1" t="inlineStr"/>
@@ -6652,7 +6428,7 @@
       <c r="M151" s="1" t="inlineStr"/>
       <c r="N151" s="1" t="inlineStr">
         <is>
-          <t>L1051: symbol-only separator/garbage line :: 5, 20</t>
+          <t>L1026: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O151" s="1" t="inlineStr"/>
@@ -6683,7 +6459,7 @@
       <c r="M152" s="1" t="inlineStr"/>
       <c r="N152" s="1" t="inlineStr">
         <is>
-          <t>L1055: isolated marker/symbol line :: .</t>
+          <t>L1027: symbol-only separator/garbage line :: 11.</t>
         </is>
       </c>
       <c r="O152" s="1" t="inlineStr"/>
@@ -6714,7 +6490,7 @@
       <c r="M153" s="1" t="inlineStr"/>
       <c r="N153" s="1" t="inlineStr">
         <is>
-          <t>L1056: isolated marker/symbol line :: .</t>
+          <t>L1030: isolated marker/symbol line :: 451</t>
         </is>
       </c>
       <c r="O153" s="1" t="inlineStr"/>
@@ -6745,7 +6521,7 @@
       <c r="M154" s="1" t="inlineStr"/>
       <c r="N154" s="1" t="inlineStr">
         <is>
-          <t>L1057: symbol-only separator/garbage line :: 20, 00</t>
+          <t>L1032: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="O154" s="1" t="inlineStr"/>
@@ -6776,7 +6552,7 @@
       <c r="M155" s="1" t="inlineStr"/>
       <c r="N155" s="1" t="inlineStr">
         <is>
-          <t>L1058: isolated marker/symbol line :: i</t>
+          <t>L1033: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O155" s="1" t="inlineStr"/>
@@ -6807,7 +6583,7 @@
       <c r="M156" s="1" t="inlineStr"/>
       <c r="N156" s="1" t="inlineStr">
         <is>
-          <t>L1059: isolated marker/symbol line :: '</t>
+          <t>L1035: symbol-only separator/garbage line :: 7.10</t>
         </is>
       </c>
       <c r="O156" s="1" t="inlineStr"/>
@@ -6838,7 +6614,7 @@
       <c r="M157" s="1" t="inlineStr"/>
       <c r="N157" s="1" t="inlineStr">
         <is>
-          <t>L1062: isolated marker/symbol line :: 8</t>
+          <t>L1037: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O157" s="1" t="inlineStr"/>
@@ -6869,7 +6645,7 @@
       <c r="M158" s="1" t="inlineStr"/>
       <c r="N158" s="1" t="inlineStr">
         <is>
-          <t>L1063: isolated marker/symbol line :: 1</t>
+          <t>L1039: symbol-only separator/garbage line :: 2, 00</t>
         </is>
       </c>
       <c r="O158" s="1" t="inlineStr"/>
@@ -6900,7 +6676,7 @@
       <c r="M159" s="1" t="inlineStr"/>
       <c r="N159" s="1" t="inlineStr">
         <is>
-          <t>L1065: symbol-only separator/garbage line :: 2, 90</t>
+          <t>L1041: symbol-only separator/garbage line :: 6, 60</t>
         </is>
       </c>
       <c r="O159" s="1" t="inlineStr"/>
@@ -6931,7 +6707,7 @@
       <c r="M160" s="1" t="inlineStr"/>
       <c r="N160" s="1" t="inlineStr">
         <is>
-          <t>L1067: isolated marker/symbol line :: 1</t>
+          <t>L1043: symbol-only separator/garbage line :: $116, 371</t>
         </is>
       </c>
       <c r="O160" s="1" t="inlineStr"/>
@@ -6962,7 +6738,7 @@
       <c r="M161" s="1" t="inlineStr"/>
       <c r="N161" s="1" t="inlineStr">
         <is>
-          <t>L1071: symbol-only separator/garbage line :: 220.00</t>
+          <t>L1046: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O161" s="1" t="inlineStr"/>
@@ -6993,7 +6769,7 @@
       <c r="M162" s="1" t="inlineStr"/>
       <c r="N162" s="1" t="inlineStr">
         <is>
-          <t>L1075: symbol-only separator/garbage line :: 3.00</t>
+          <t>L1048: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O162" s="1" t="inlineStr"/>
@@ -7024,7 +6800,7 @@
       <c r="M163" s="1" t="inlineStr"/>
       <c r="N163" s="1" t="inlineStr">
         <is>
-          <t>L1077: symbol-only separator/garbage line :: 7.55</t>
+          <t>L1051: symbol-only separator/garbage line :: 5, 20</t>
         </is>
       </c>
       <c r="O163" s="1" t="inlineStr"/>
@@ -7055,7 +6831,7 @@
       <c r="M164" s="1" t="inlineStr"/>
       <c r="N164" s="1" t="inlineStr">
         <is>
-          <t>L1078: isolated marker/symbol line :: å‡†</t>
+          <t>L1055: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O164" s="1" t="inlineStr"/>
@@ -7086,7 +6862,7 @@
       <c r="M165" s="1" t="inlineStr"/>
       <c r="N165" s="1" t="inlineStr">
         <is>
-          <t>L1080: symbol-only separator/garbage line :: 50.00</t>
+          <t>L1056: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O165" s="1" t="inlineStr"/>
@@ -7117,7 +6893,7 @@
       <c r="M166" s="1" t="inlineStr"/>
       <c r="N166" s="1" t="inlineStr">
         <is>
-          <t>L1081: isolated marker/symbol line :: :</t>
+          <t>L1057: symbol-only separator/garbage line :: 20, 00</t>
         </is>
       </c>
       <c r="O166" s="1" t="inlineStr"/>
@@ -7148,7 +6924,7 @@
       <c r="M167" s="1" t="inlineStr"/>
       <c r="N167" s="1" t="inlineStr">
         <is>
-          <t>L1083: symbol-only separator/garbage line :: 9, 16</t>
+          <t>L1058: isolated marker/symbol line :: i</t>
         </is>
       </c>
       <c r="O167" s="1" t="inlineStr"/>
@@ -7179,7 +6955,7 @@
       <c r="M168" s="1" t="inlineStr"/>
       <c r="N168" s="1" t="inlineStr">
         <is>
-          <t>L1085: isolated marker/symbol line :: F</t>
+          <t>L1059: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O168" s="1" t="inlineStr"/>
@@ -7210,7 +6986,7 @@
       <c r="M169" s="1" t="inlineStr"/>
       <c r="N169" s="1" t="inlineStr">
         <is>
-          <t>L1086: isolated marker/symbol line :: F</t>
+          <t>L1062: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O169" s="1" t="inlineStr"/>
@@ -7241,7 +7017,7 @@
       <c r="M170" s="1" t="inlineStr"/>
       <c r="N170" s="1" t="inlineStr">
         <is>
-          <t>L1088: isolated marker/symbol line :: 3</t>
+          <t>L1063: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O170" s="1" t="inlineStr"/>
@@ -7272,7 +7048,7 @@
       <c r="M171" s="1" t="inlineStr"/>
       <c r="N171" s="1" t="inlineStr">
         <is>
-          <t>L1089: isolated marker/symbol line :: 370</t>
+          <t>L1065: symbol-only separator/garbage line :: 2, 90</t>
         </is>
       </c>
       <c r="O171" s="1" t="inlineStr"/>
@@ -7303,7 +7079,7 @@
       <c r="M172" s="1" t="inlineStr"/>
       <c r="N172" s="1" t="inlineStr">
         <is>
-          <t>L1091: isolated marker/symbol line :: 8</t>
+          <t>L1067: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O172" s="1" t="inlineStr"/>
@@ -7334,7 +7110,7 @@
       <c r="M173" s="1" t="inlineStr"/>
       <c r="N173" s="1" t="inlineStr">
         <is>
-          <t>L1095: isolated marker/symbol line :: .</t>
+          <t>L1071: symbol-only separator/garbage line :: 220.00</t>
         </is>
       </c>
       <c r="O173" s="1" t="inlineStr"/>
@@ -7365,7 +7141,7 @@
       <c r="M174" s="1" t="inlineStr"/>
       <c r="N174" s="1" t="inlineStr">
         <is>
-          <t>L1099: symbol-only separator/garbage line :: 24.00</t>
+          <t>L1075: symbol-only separator/garbage line :: 3.00</t>
         </is>
       </c>
       <c r="O174" s="1" t="inlineStr"/>
@@ -7396,7 +7172,7 @@
       <c r="M175" s="1" t="inlineStr"/>
       <c r="N175" s="1" t="inlineStr">
         <is>
-          <t>L1104: isolated marker/symbol line :: 2</t>
+          <t>L1077: symbol-only separator/garbage line :: 7.55</t>
         </is>
       </c>
       <c r="O175" s="1" t="inlineStr"/>
@@ -7427,7 +7203,7 @@
       <c r="M176" s="1" t="inlineStr"/>
       <c r="N176" s="1" t="inlineStr">
         <is>
-          <t>L1106: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L1078: stray/suspicious non-ASCII glyph(s): U+51C6 CJK UNIFIED IDEOGRAPH-51C6 | isolated marker/symbol line :: 准</t>
         </is>
       </c>
       <c r="O176" s="1" t="inlineStr"/>
@@ -7458,7 +7234,7 @@
       <c r="M177" s="1" t="inlineStr"/>
       <c r="N177" s="1" t="inlineStr">
         <is>
-          <t>L1107: isolated marker/symbol line :: 1</t>
+          <t>L1080: symbol-only separator/garbage line :: 50.00</t>
         </is>
       </c>
       <c r="O177" s="1" t="inlineStr"/>
@@ -7489,7 +7265,7 @@
       <c r="M178" s="1" t="inlineStr"/>
       <c r="N178" s="1" t="inlineStr">
         <is>
-          <t>L1108: isolated marker/symbol line :: P</t>
+          <t>L1081: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O178" s="1" t="inlineStr"/>
@@ -7520,7 +7296,7 @@
       <c r="M179" s="1" t="inlineStr"/>
       <c r="N179" s="1" t="inlineStr">
         <is>
-          <t>L1109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L1083: symbol-only separator/garbage line :: 9, 16</t>
         </is>
       </c>
       <c r="O179" s="1" t="inlineStr"/>
@@ -7551,7 +7327,7 @@
       <c r="M180" s="1" t="inlineStr"/>
       <c r="N180" s="1" t="inlineStr">
         <is>
-          <t>L1110: isolated marker/symbol line :: 0</t>
+          <t>L1085: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="O180" s="1" t="inlineStr"/>
@@ -7582,7 +7358,7 @@
       <c r="M181" s="1" t="inlineStr"/>
       <c r="N181" s="1" t="inlineStr">
         <is>
-          <t>L1112: isolated marker/symbol line :: 5</t>
+          <t>L1086: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="O181" s="1" t="inlineStr"/>
@@ -7597,6 +7373,409 @@
       <c r="X181" s="1" t="inlineStr"/>
       <c r="Y181" s="1" t="inlineStr"/>
     </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr"/>
+      <c r="B182" s="1" t="inlineStr"/>
+      <c r="C182" s="1" t="inlineStr"/>
+      <c r="D182" s="1" t="inlineStr"/>
+      <c r="E182" s="1" t="inlineStr"/>
+      <c r="F182" s="1" t="inlineStr"/>
+      <c r="G182" s="1" t="inlineStr"/>
+      <c r="H182" s="1" t="inlineStr"/>
+      <c r="I182" s="1" t="inlineStr"/>
+      <c r="J182" s="1" t="inlineStr"/>
+      <c r="K182" s="1" t="inlineStr"/>
+      <c r="L182" s="1" t="inlineStr"/>
+      <c r="M182" s="1" t="inlineStr"/>
+      <c r="N182" s="1" t="inlineStr">
+        <is>
+          <t>L1088: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
+      <c r="O182" s="1" t="inlineStr"/>
+      <c r="P182" s="1" t="inlineStr"/>
+      <c r="Q182" s="1" t="inlineStr"/>
+      <c r="R182" s="1" t="inlineStr"/>
+      <c r="S182" s="1" t="inlineStr"/>
+      <c r="T182" s="1" t="inlineStr"/>
+      <c r="U182" s="1" t="inlineStr"/>
+      <c r="V182" s="1" t="inlineStr"/>
+      <c r="W182" s="1" t="inlineStr"/>
+      <c r="X182" s="1" t="inlineStr"/>
+      <c r="Y182" s="1" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr"/>
+      <c r="B183" s="1" t="inlineStr"/>
+      <c r="C183" s="1" t="inlineStr"/>
+      <c r="D183" s="1" t="inlineStr"/>
+      <c r="E183" s="1" t="inlineStr"/>
+      <c r="F183" s="1" t="inlineStr"/>
+      <c r="G183" s="1" t="inlineStr"/>
+      <c r="H183" s="1" t="inlineStr"/>
+      <c r="I183" s="1" t="inlineStr"/>
+      <c r="J183" s="1" t="inlineStr"/>
+      <c r="K183" s="1" t="inlineStr"/>
+      <c r="L183" s="1" t="inlineStr"/>
+      <c r="M183" s="1" t="inlineStr"/>
+      <c r="N183" s="1" t="inlineStr">
+        <is>
+          <t>L1089: isolated marker/symbol line :: 370</t>
+        </is>
+      </c>
+      <c r="O183" s="1" t="inlineStr"/>
+      <c r="P183" s="1" t="inlineStr"/>
+      <c r="Q183" s="1" t="inlineStr"/>
+      <c r="R183" s="1" t="inlineStr"/>
+      <c r="S183" s="1" t="inlineStr"/>
+      <c r="T183" s="1" t="inlineStr"/>
+      <c r="U183" s="1" t="inlineStr"/>
+      <c r="V183" s="1" t="inlineStr"/>
+      <c r="W183" s="1" t="inlineStr"/>
+      <c r="X183" s="1" t="inlineStr"/>
+      <c r="Y183" s="1" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr"/>
+      <c r="B184" s="1" t="inlineStr"/>
+      <c r="C184" s="1" t="inlineStr"/>
+      <c r="D184" s="1" t="inlineStr"/>
+      <c r="E184" s="1" t="inlineStr"/>
+      <c r="F184" s="1" t="inlineStr"/>
+      <c r="G184" s="1" t="inlineStr"/>
+      <c r="H184" s="1" t="inlineStr"/>
+      <c r="I184" s="1" t="inlineStr"/>
+      <c r="J184" s="1" t="inlineStr"/>
+      <c r="K184" s="1" t="inlineStr"/>
+      <c r="L184" s="1" t="inlineStr"/>
+      <c r="M184" s="1" t="inlineStr"/>
+      <c r="N184" s="1" t="inlineStr">
+        <is>
+          <t>L1091: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O184" s="1" t="inlineStr"/>
+      <c r="P184" s="1" t="inlineStr"/>
+      <c r="Q184" s="1" t="inlineStr"/>
+      <c r="R184" s="1" t="inlineStr"/>
+      <c r="S184" s="1" t="inlineStr"/>
+      <c r="T184" s="1" t="inlineStr"/>
+      <c r="U184" s="1" t="inlineStr"/>
+      <c r="V184" s="1" t="inlineStr"/>
+      <c r="W184" s="1" t="inlineStr"/>
+      <c r="X184" s="1" t="inlineStr"/>
+      <c r="Y184" s="1" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr"/>
+      <c r="B185" s="1" t="inlineStr"/>
+      <c r="C185" s="1" t="inlineStr"/>
+      <c r="D185" s="1" t="inlineStr"/>
+      <c r="E185" s="1" t="inlineStr"/>
+      <c r="F185" s="1" t="inlineStr"/>
+      <c r="G185" s="1" t="inlineStr"/>
+      <c r="H185" s="1" t="inlineStr"/>
+      <c r="I185" s="1" t="inlineStr"/>
+      <c r="J185" s="1" t="inlineStr"/>
+      <c r="K185" s="1" t="inlineStr"/>
+      <c r="L185" s="1" t="inlineStr"/>
+      <c r="M185" s="1" t="inlineStr"/>
+      <c r="N185" s="1" t="inlineStr">
+        <is>
+          <t>L1092: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="O185" s="1" t="inlineStr"/>
+      <c r="P185" s="1" t="inlineStr"/>
+      <c r="Q185" s="1" t="inlineStr"/>
+      <c r="R185" s="1" t="inlineStr"/>
+      <c r="S185" s="1" t="inlineStr"/>
+      <c r="T185" s="1" t="inlineStr"/>
+      <c r="U185" s="1" t="inlineStr"/>
+      <c r="V185" s="1" t="inlineStr"/>
+      <c r="W185" s="1" t="inlineStr"/>
+      <c r="X185" s="1" t="inlineStr"/>
+      <c r="Y185" s="1" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr"/>
+      <c r="B186" s="1" t="inlineStr"/>
+      <c r="C186" s="1" t="inlineStr"/>
+      <c r="D186" s="1" t="inlineStr"/>
+      <c r="E186" s="1" t="inlineStr"/>
+      <c r="F186" s="1" t="inlineStr"/>
+      <c r="G186" s="1" t="inlineStr"/>
+      <c r="H186" s="1" t="inlineStr"/>
+      <c r="I186" s="1" t="inlineStr"/>
+      <c r="J186" s="1" t="inlineStr"/>
+      <c r="K186" s="1" t="inlineStr"/>
+      <c r="L186" s="1" t="inlineStr"/>
+      <c r="M186" s="1" t="inlineStr"/>
+      <c r="N186" s="1" t="inlineStr">
+        <is>
+          <t>L1095: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O186" s="1" t="inlineStr"/>
+      <c r="P186" s="1" t="inlineStr"/>
+      <c r="Q186" s="1" t="inlineStr"/>
+      <c r="R186" s="1" t="inlineStr"/>
+      <c r="S186" s="1" t="inlineStr"/>
+      <c r="T186" s="1" t="inlineStr"/>
+      <c r="U186" s="1" t="inlineStr"/>
+      <c r="V186" s="1" t="inlineStr"/>
+      <c r="W186" s="1" t="inlineStr"/>
+      <c r="X186" s="1" t="inlineStr"/>
+      <c r="Y186" s="1" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr"/>
+      <c r="B187" s="1" t="inlineStr"/>
+      <c r="C187" s="1" t="inlineStr"/>
+      <c r="D187" s="1" t="inlineStr"/>
+      <c r="E187" s="1" t="inlineStr"/>
+      <c r="F187" s="1" t="inlineStr"/>
+      <c r="G187" s="1" t="inlineStr"/>
+      <c r="H187" s="1" t="inlineStr"/>
+      <c r="I187" s="1" t="inlineStr"/>
+      <c r="J187" s="1" t="inlineStr"/>
+      <c r="K187" s="1" t="inlineStr"/>
+      <c r="L187" s="1" t="inlineStr"/>
+      <c r="M187" s="1" t="inlineStr"/>
+      <c r="N187" s="1" t="inlineStr">
+        <is>
+          <t>L1099: symbol-only separator/garbage line :: 24.00</t>
+        </is>
+      </c>
+      <c r="O187" s="1" t="inlineStr"/>
+      <c r="P187" s="1" t="inlineStr"/>
+      <c r="Q187" s="1" t="inlineStr"/>
+      <c r="R187" s="1" t="inlineStr"/>
+      <c r="S187" s="1" t="inlineStr"/>
+      <c r="T187" s="1" t="inlineStr"/>
+      <c r="U187" s="1" t="inlineStr"/>
+      <c r="V187" s="1" t="inlineStr"/>
+      <c r="W187" s="1" t="inlineStr"/>
+      <c r="X187" s="1" t="inlineStr"/>
+      <c r="Y187" s="1" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr"/>
+      <c r="B188" s="1" t="inlineStr"/>
+      <c r="C188" s="1" t="inlineStr"/>
+      <c r="D188" s="1" t="inlineStr"/>
+      <c r="E188" s="1" t="inlineStr"/>
+      <c r="F188" s="1" t="inlineStr"/>
+      <c r="G188" s="1" t="inlineStr"/>
+      <c r="H188" s="1" t="inlineStr"/>
+      <c r="I188" s="1" t="inlineStr"/>
+      <c r="J188" s="1" t="inlineStr"/>
+      <c r="K188" s="1" t="inlineStr"/>
+      <c r="L188" s="1" t="inlineStr"/>
+      <c r="M188" s="1" t="inlineStr"/>
+      <c r="N188" s="1" t="inlineStr">
+        <is>
+          <t>L1104: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O188" s="1" t="inlineStr"/>
+      <c r="P188" s="1" t="inlineStr"/>
+      <c r="Q188" s="1" t="inlineStr"/>
+      <c r="R188" s="1" t="inlineStr"/>
+      <c r="S188" s="1" t="inlineStr"/>
+      <c r="T188" s="1" t="inlineStr"/>
+      <c r="U188" s="1" t="inlineStr"/>
+      <c r="V188" s="1" t="inlineStr"/>
+      <c r="W188" s="1" t="inlineStr"/>
+      <c r="X188" s="1" t="inlineStr"/>
+      <c r="Y188" s="1" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr"/>
+      <c r="B189" s="1" t="inlineStr"/>
+      <c r="C189" s="1" t="inlineStr"/>
+      <c r="D189" s="1" t="inlineStr"/>
+      <c r="E189" s="1" t="inlineStr"/>
+      <c r="F189" s="1" t="inlineStr"/>
+      <c r="G189" s="1" t="inlineStr"/>
+      <c r="H189" s="1" t="inlineStr"/>
+      <c r="I189" s="1" t="inlineStr"/>
+      <c r="J189" s="1" t="inlineStr"/>
+      <c r="K189" s="1" t="inlineStr"/>
+      <c r="L189" s="1" t="inlineStr"/>
+      <c r="M189" s="1" t="inlineStr"/>
+      <c r="N189" s="1" t="inlineStr">
+        <is>
+          <t>L1106: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="O189" s="1" t="inlineStr"/>
+      <c r="P189" s="1" t="inlineStr"/>
+      <c r="Q189" s="1" t="inlineStr"/>
+      <c r="R189" s="1" t="inlineStr"/>
+      <c r="S189" s="1" t="inlineStr"/>
+      <c r="T189" s="1" t="inlineStr"/>
+      <c r="U189" s="1" t="inlineStr"/>
+      <c r="V189" s="1" t="inlineStr"/>
+      <c r="W189" s="1" t="inlineStr"/>
+      <c r="X189" s="1" t="inlineStr"/>
+      <c r="Y189" s="1" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr"/>
+      <c r="B190" s="1" t="inlineStr"/>
+      <c r="C190" s="1" t="inlineStr"/>
+      <c r="D190" s="1" t="inlineStr"/>
+      <c r="E190" s="1" t="inlineStr"/>
+      <c r="F190" s="1" t="inlineStr"/>
+      <c r="G190" s="1" t="inlineStr"/>
+      <c r="H190" s="1" t="inlineStr"/>
+      <c r="I190" s="1" t="inlineStr"/>
+      <c r="J190" s="1" t="inlineStr"/>
+      <c r="K190" s="1" t="inlineStr"/>
+      <c r="L190" s="1" t="inlineStr"/>
+      <c r="M190" s="1" t="inlineStr"/>
+      <c r="N190" s="1" t="inlineStr">
+        <is>
+          <t>L1107: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O190" s="1" t="inlineStr"/>
+      <c r="P190" s="1" t="inlineStr"/>
+      <c r="Q190" s="1" t="inlineStr"/>
+      <c r="R190" s="1" t="inlineStr"/>
+      <c r="S190" s="1" t="inlineStr"/>
+      <c r="T190" s="1" t="inlineStr"/>
+      <c r="U190" s="1" t="inlineStr"/>
+      <c r="V190" s="1" t="inlineStr"/>
+      <c r="W190" s="1" t="inlineStr"/>
+      <c r="X190" s="1" t="inlineStr"/>
+      <c r="Y190" s="1" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr"/>
+      <c r="B191" s="1" t="inlineStr"/>
+      <c r="C191" s="1" t="inlineStr"/>
+      <c r="D191" s="1" t="inlineStr"/>
+      <c r="E191" s="1" t="inlineStr"/>
+      <c r="F191" s="1" t="inlineStr"/>
+      <c r="G191" s="1" t="inlineStr"/>
+      <c r="H191" s="1" t="inlineStr"/>
+      <c r="I191" s="1" t="inlineStr"/>
+      <c r="J191" s="1" t="inlineStr"/>
+      <c r="K191" s="1" t="inlineStr"/>
+      <c r="L191" s="1" t="inlineStr"/>
+      <c r="M191" s="1" t="inlineStr"/>
+      <c r="N191" s="1" t="inlineStr">
+        <is>
+          <t>L1108: isolated marker/symbol line :: P</t>
+        </is>
+      </c>
+      <c r="O191" s="1" t="inlineStr"/>
+      <c r="P191" s="1" t="inlineStr"/>
+      <c r="Q191" s="1" t="inlineStr"/>
+      <c r="R191" s="1" t="inlineStr"/>
+      <c r="S191" s="1" t="inlineStr"/>
+      <c r="T191" s="1" t="inlineStr"/>
+      <c r="U191" s="1" t="inlineStr"/>
+      <c r="V191" s="1" t="inlineStr"/>
+      <c r="W191" s="1" t="inlineStr"/>
+      <c r="X191" s="1" t="inlineStr"/>
+      <c r="Y191" s="1" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr"/>
+      <c r="B192" s="1" t="inlineStr"/>
+      <c r="C192" s="1" t="inlineStr"/>
+      <c r="D192" s="1" t="inlineStr"/>
+      <c r="E192" s="1" t="inlineStr"/>
+      <c r="F192" s="1" t="inlineStr"/>
+      <c r="G192" s="1" t="inlineStr"/>
+      <c r="H192" s="1" t="inlineStr"/>
+      <c r="I192" s="1" t="inlineStr"/>
+      <c r="J192" s="1" t="inlineStr"/>
+      <c r="K192" s="1" t="inlineStr"/>
+      <c r="L192" s="1" t="inlineStr"/>
+      <c r="M192" s="1" t="inlineStr"/>
+      <c r="N192" s="1" t="inlineStr">
+        <is>
+          <t>L1109: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="O192" s="1" t="inlineStr"/>
+      <c r="P192" s="1" t="inlineStr"/>
+      <c r="Q192" s="1" t="inlineStr"/>
+      <c r="R192" s="1" t="inlineStr"/>
+      <c r="S192" s="1" t="inlineStr"/>
+      <c r="T192" s="1" t="inlineStr"/>
+      <c r="U192" s="1" t="inlineStr"/>
+      <c r="V192" s="1" t="inlineStr"/>
+      <c r="W192" s="1" t="inlineStr"/>
+      <c r="X192" s="1" t="inlineStr"/>
+      <c r="Y192" s="1" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr"/>
+      <c r="B193" s="1" t="inlineStr"/>
+      <c r="C193" s="1" t="inlineStr"/>
+      <c r="D193" s="1" t="inlineStr"/>
+      <c r="E193" s="1" t="inlineStr"/>
+      <c r="F193" s="1" t="inlineStr"/>
+      <c r="G193" s="1" t="inlineStr"/>
+      <c r="H193" s="1" t="inlineStr"/>
+      <c r="I193" s="1" t="inlineStr"/>
+      <c r="J193" s="1" t="inlineStr"/>
+      <c r="K193" s="1" t="inlineStr"/>
+      <c r="L193" s="1" t="inlineStr"/>
+      <c r="M193" s="1" t="inlineStr"/>
+      <c r="N193" s="1" t="inlineStr">
+        <is>
+          <t>L1110: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
+      <c r="O193" s="1" t="inlineStr"/>
+      <c r="P193" s="1" t="inlineStr"/>
+      <c r="Q193" s="1" t="inlineStr"/>
+      <c r="R193" s="1" t="inlineStr"/>
+      <c r="S193" s="1" t="inlineStr"/>
+      <c r="T193" s="1" t="inlineStr"/>
+      <c r="U193" s="1" t="inlineStr"/>
+      <c r="V193" s="1" t="inlineStr"/>
+      <c r="W193" s="1" t="inlineStr"/>
+      <c r="X193" s="1" t="inlineStr"/>
+      <c r="Y193" s="1" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr"/>
+      <c r="B194" s="1" t="inlineStr"/>
+      <c r="C194" s="1" t="inlineStr"/>
+      <c r="D194" s="1" t="inlineStr"/>
+      <c r="E194" s="1" t="inlineStr"/>
+      <c r="F194" s="1" t="inlineStr"/>
+      <c r="G194" s="1" t="inlineStr"/>
+      <c r="H194" s="1" t="inlineStr"/>
+      <c r="I194" s="1" t="inlineStr"/>
+      <c r="J194" s="1" t="inlineStr"/>
+      <c r="K194" s="1" t="inlineStr"/>
+      <c r="L194" s="1" t="inlineStr"/>
+      <c r="M194" s="1" t="inlineStr"/>
+      <c r="N194" s="1" t="inlineStr">
+        <is>
+          <t>L1112: isolated marker/symbol line :: 5</t>
+        </is>
+      </c>
+      <c r="O194" s="1" t="inlineStr"/>
+      <c r="P194" s="1" t="inlineStr"/>
+      <c r="Q194" s="1" t="inlineStr"/>
+      <c r="R194" s="1" t="inlineStr"/>
+      <c r="S194" s="1" t="inlineStr"/>
+      <c r="T194" s="1" t="inlineStr"/>
+      <c r="U194" s="1" t="inlineStr"/>
+      <c r="V194" s="1" t="inlineStr"/>
+      <c r="W194" s="1" t="inlineStr"/>
+      <c r="X194" s="1" t="inlineStr"/>
+      <c r="Y194" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
